--- a/tools/importer/reports/import-linzess-faq.report.xlsx
+++ b/tools/importer/reports/import-linzess-faq.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>_reportFile</t>
   </si>
@@ -40,7 +40,7 @@
     <t>savings-and-support/community-support.report.json</t>
   </si>
   <si>
-    <t>["hero","cards","cards","cards","cards","brightcove-video","columns","columns","columns","columns","columns"]</t>
+    <t>["columns","columns","columns","columns","columns","columns"]</t>
   </si>
   <si>
     <t>savings-and-support/community-support</t>
@@ -49,10 +49,10 @@
     <t>success</t>
   </si>
   <si>
-    <t>linzess-community-support</t>
-  </si>
-  <si>
-    <t>2026-06-02T14:43:17.559Z</t>
+    <t>linzess-faq</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:30:21.032Z</t>
   </si>
   <si>
     <t>Resources &amp; Helpful Information | LINZESS® (linaclotide)</t>
@@ -70,9 +70,6 @@
     <t>savings-and-support/faqs</t>
   </si>
   <si>
-    <t>linzess-faq</t>
-  </si>
-  <si>
     <t>2026-06-02T17:09:21.594Z</t>
   </si>
   <si>
@@ -109,7 +106,7 @@
     <t>savings-and-support/how-to-take-linzess</t>
   </si>
   <si>
-    <t>2026-06-02T14:30:40.496Z</t>
+    <t>2026-06-08T08:30:29.625Z</t>
   </si>
   <si>
     <t>Find Relief | LINZESS® (linaclotide)</t>
@@ -509,7 +506,7 @@
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="41" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
@@ -580,68 +577,68 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>33</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-linzess-faq.report.xlsx
+++ b/tools/importer/reports/import-linzess-faq.report.xlsx
@@ -70,7 +70,7 @@
     <t>savings-and-support/faqs</t>
   </si>
   <si>
-    <t>2026-06-02T17:09:21.594Z</t>
+    <t>2026-06-14T14:08:44.306Z</t>
   </si>
   <si>
     <t>Frequently Asked Questions | LINZESS® (linaclotide)</t>
